--- a/erp-server/erp-server-wms/src/main/resources/excel/warehouseLocationSuggestAfterSalesExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/warehouseLocationSuggestAfterSalesExport.xlsx
@@ -37,10 +37,10 @@
     <t>sku编码</t>
   </si>
   <si>
+    <t>EAN码</t>
+  </si>
+  <si>
     <t>产品名称</t>
-  </si>
-  <si>
-    <t>EAN码</t>
   </si>
   <si>
     <t>所属仓库</t>
@@ -1353,7 +1353,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1376,7 +1376,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="A1:B1">
+  <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>23</v>
